--- a/artfynd/A 54849-2022 artfynd.xlsx
+++ b/artfynd/A 54849-2022 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>121068062</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54849-2022 artfynd.xlsx
+++ b/artfynd/A 54849-2022 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>120442222</v>
       </c>
       <c r="B2" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -799,12 +794,7 @@
         <v>120659084</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,12 +909,7 @@
         <v>121068062</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54849-2022 artfynd.xlsx
+++ b/artfynd/A 54849-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442222</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120659084</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,8 +1037,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121068062</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>